--- a/data/all_datasets/REDD/REDD_House6_stats/2026-04-21.xlsx
+++ b/data/all_datasets/REDD/REDD_House6_stats/2026-04-21.xlsx
@@ -757,10 +757,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.994509530793994</v>
+        <v>12.90529052105171</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8232589707004743</v>
+        <v>0.8698471835812384</v>
       </c>
     </row>
     <row r="3">
@@ -773,7 +773,7 @@
         <v>0.7982009380583682</v>
       </c>
       <c r="C3" t="n">
-        <v>0.07305857872831417</v>
+        <v>0.0538006360081068</v>
       </c>
     </row>
     <row r="4">
@@ -786,7 +786,7 @@
         <v>0.7650617641766201</v>
       </c>
       <c r="C4" t="n">
-        <v>0.07002538141095654</v>
+        <v>0.05156697710517662</v>
       </c>
     </row>
     <row r="5">
@@ -799,7 +799,7 @@
         <v>0.3677200493581365</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03365706916025509</v>
+        <v>0.02478520330547832</v>
       </c>
     </row>
   </sheetData>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.994509530793994</v>
+        <v>12.90529052105171</v>
       </c>
     </row>
     <row r="3">
@@ -924,7 +924,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -941,7 +941,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -958,7 +958,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -975,7 +975,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -992,7 +992,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -1009,7 +1009,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -1026,7 +1026,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -1043,7 +1043,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -1060,7 +1060,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -1077,7 +1077,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -1094,7 +1094,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
@@ -1111,7 +1111,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
@@ -1128,7 +1128,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
@@ -1145,7 +1145,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
@@ -1162,7 +1162,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
@@ -1179,7 +1179,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
@@ -1196,7 +1196,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
@@ -1213,7 +1213,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -1230,7 +1230,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
@@ -1247,7 +1247,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C21" t="n">
         <v>0</v>
@@ -1264,7 +1264,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C22" t="n">
         <v>0</v>
@@ -1281,7 +1281,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C23" t="n">
         <v>0</v>
@@ -1298,7 +1298,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C24" t="n">
         <v>0</v>
@@ -1315,7 +1315,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
@@ -1332,7 +1332,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C26" t="n">
         <v>0</v>
@@ -1349,7 +1349,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C27" t="n">
         <v>0</v>
@@ -1366,7 +1366,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C28" t="n">
         <v>0</v>
@@ -1383,7 +1383,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
@@ -1400,7 +1400,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C30" t="n">
         <v>0</v>
@@ -1417,7 +1417,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C31" t="n">
         <v>0</v>
@@ -1434,7 +1434,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C32" t="n">
         <v>0</v>
@@ -1451,7 +1451,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C33" t="n">
         <v>0</v>
@@ -1468,7 +1468,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C34" t="n">
         <v>0</v>
@@ -1485,7 +1485,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C35" t="n">
         <v>0</v>
@@ -1502,7 +1502,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C36" t="n">
         <v>0</v>
@@ -1519,7 +1519,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C37" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
@@ -1553,7 +1553,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C39" t="n">
         <v>0</v>
@@ -1570,7 +1570,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C40" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C41" t="n">
         <v>0</v>
@@ -1604,7 +1604,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C42" t="n">
         <v>0</v>
@@ -1621,7 +1621,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C43" t="n">
         <v>0</v>
@@ -1638,7 +1638,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C44" t="n">
         <v>0</v>
@@ -1655,7 +1655,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C45" t="n">
         <v>0</v>
@@ -1672,7 +1672,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C46" t="n">
         <v>0</v>
@@ -1689,7 +1689,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C47" t="n">
         <v>0</v>
@@ -1706,7 +1706,7 @@
         <v>46</v>
       </c>
       <c r="B48" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C48" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
         <v>47</v>
       </c>
       <c r="B49" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C49" t="n">
         <v>0</v>
@@ -1740,7 +1740,7 @@
         <v>48</v>
       </c>
       <c r="B50" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C50" t="n">
         <v>0</v>
@@ -1757,7 +1757,7 @@
         <v>49</v>
       </c>
       <c r="B51" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C51" t="n">
         <v>0</v>
@@ -1774,7 +1774,7 @@
         <v>50</v>
       </c>
       <c r="B52" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C52" t="n">
         <v>0</v>
@@ -1791,7 +1791,7 @@
         <v>51</v>
       </c>
       <c r="B53" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C53" t="n">
         <v>0</v>
@@ -1808,7 +1808,7 @@
         <v>52</v>
       </c>
       <c r="B54" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C54" t="n">
         <v>0</v>
@@ -1825,7 +1825,7 @@
         <v>53</v>
       </c>
       <c r="B55" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C55" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
         <v>54</v>
       </c>
       <c r="B56" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C56" t="n">
         <v>0</v>
@@ -1859,7 +1859,7 @@
         <v>55</v>
       </c>
       <c r="B57" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C57" t="n">
         <v>0</v>
@@ -1876,7 +1876,7 @@
         <v>56</v>
       </c>
       <c r="B58" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C58" t="n">
         <v>0</v>
@@ -1893,7 +1893,7 @@
         <v>57</v>
       </c>
       <c r="B59" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C59" t="n">
         <v>0</v>
@@ -1910,7 +1910,7 @@
         <v>58</v>
       </c>
       <c r="B60" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C60" t="n">
         <v>0</v>
@@ -1927,7 +1927,7 @@
         <v>59</v>
       </c>
       <c r="B61" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C61" t="n">
         <v>0</v>
@@ -1944,7 +1944,7 @@
         <v>60</v>
       </c>
       <c r="B62" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C62" t="n">
         <v>0</v>
@@ -1961,7 +1961,7 @@
         <v>61</v>
       </c>
       <c r="B63" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C63" t="n">
         <v>0</v>
@@ -1978,7 +1978,7 @@
         <v>62</v>
       </c>
       <c r="B64" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C64" t="n">
         <v>0</v>
@@ -1995,7 +1995,7 @@
         <v>63</v>
       </c>
       <c r="B65" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C65" t="n">
         <v>0</v>
@@ -2012,7 +2012,7 @@
         <v>64</v>
       </c>
       <c r="B66" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C66" t="n">
         <v>0</v>
@@ -2029,7 +2029,7 @@
         <v>65</v>
       </c>
       <c r="B67" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C67" t="n">
         <v>0</v>
@@ -2046,7 +2046,7 @@
         <v>66</v>
       </c>
       <c r="B68" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C68" t="n">
         <v>0</v>
@@ -2063,7 +2063,7 @@
         <v>67</v>
       </c>
       <c r="B69" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C69" t="n">
         <v>0</v>
@@ -2080,7 +2080,7 @@
         <v>68</v>
       </c>
       <c r="B70" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C70" t="n">
         <v>0</v>
@@ -2097,7 +2097,7 @@
         <v>69</v>
       </c>
       <c r="B71" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C71" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
         <v>70</v>
       </c>
       <c r="B72" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C72" t="n">
         <v>0</v>
@@ -2131,7 +2131,7 @@
         <v>71</v>
       </c>
       <c r="B73" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C73" t="n">
         <v>0</v>
@@ -2148,7 +2148,7 @@
         <v>72</v>
       </c>
       <c r="B74" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C74" t="n">
         <v>0</v>
@@ -2165,7 +2165,7 @@
         <v>73</v>
       </c>
       <c r="B75" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C75" t="n">
         <v>0</v>
@@ -2182,7 +2182,7 @@
         <v>74</v>
       </c>
       <c r="B76" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C76" t="n">
         <v>0</v>
@@ -2199,7 +2199,7 @@
         <v>75</v>
       </c>
       <c r="B77" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C77" t="n">
         <v>0</v>
@@ -2216,7 +2216,7 @@
         <v>76</v>
       </c>
       <c r="B78" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C78" t="n">
         <v>0</v>
@@ -2233,7 +2233,7 @@
         <v>77</v>
       </c>
       <c r="B79" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C79" t="n">
         <v>0</v>
@@ -2250,7 +2250,7 @@
         <v>78</v>
       </c>
       <c r="B80" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C80" t="n">
         <v>0</v>
@@ -2267,7 +2267,7 @@
         <v>79</v>
       </c>
       <c r="B81" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C81" t="n">
         <v>0</v>
@@ -2284,7 +2284,7 @@
         <v>80</v>
       </c>
       <c r="B82" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
@@ -2301,7 +2301,7 @@
         <v>81</v>
       </c>
       <c r="B83" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C83" t="n">
         <v>0</v>
@@ -2318,7 +2318,7 @@
         <v>82</v>
       </c>
       <c r="B84" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C84" t="n">
         <v>0</v>
@@ -2335,7 +2335,7 @@
         <v>83</v>
       </c>
       <c r="B85" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
@@ -2352,7 +2352,7 @@
         <v>84</v>
       </c>
       <c r="B86" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
@@ -2369,7 +2369,7 @@
         <v>85</v>
       </c>
       <c r="B87" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
@@ -2386,7 +2386,7 @@
         <v>86</v>
       </c>
       <c r="B88" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
@@ -2403,7 +2403,7 @@
         <v>87</v>
       </c>
       <c r="B89" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
@@ -2420,7 +2420,7 @@
         <v>88</v>
       </c>
       <c r="B90" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
@@ -2437,7 +2437,7 @@
         <v>89</v>
       </c>
       <c r="B91" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
@@ -2454,7 +2454,7 @@
         <v>90</v>
       </c>
       <c r="B92" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
@@ -2471,7 +2471,7 @@
         <v>91</v>
       </c>
       <c r="B93" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
@@ -2488,7 +2488,7 @@
         <v>92</v>
       </c>
       <c r="B94" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
@@ -2505,7 +2505,7 @@
         <v>93</v>
       </c>
       <c r="B95" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C95" t="n">
         <v>0</v>
@@ -2522,7 +2522,7 @@
         <v>94</v>
       </c>
       <c r="B96" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C96" t="n">
         <v>0</v>
@@ -2539,7 +2539,7 @@
         <v>95</v>
       </c>
       <c r="B97" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C97" t="n">
         <v>0</v>
@@ -2556,7 +2556,7 @@
         <v>96</v>
       </c>
       <c r="B98" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C98" t="n">
         <v>0</v>
@@ -2573,7 +2573,7 @@
         <v>97</v>
       </c>
       <c r="B99" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C99" t="n">
         <v>0</v>
@@ -2590,7 +2590,7 @@
         <v>98</v>
       </c>
       <c r="B100" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C100" t="n">
         <v>0</v>
@@ -2607,7 +2607,7 @@
         <v>99</v>
       </c>
       <c r="B101" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C101" t="n">
         <v>0</v>
@@ -2624,7 +2624,7 @@
         <v>100</v>
       </c>
       <c r="B102" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C102" t="n">
         <v>0</v>
@@ -2641,7 +2641,7 @@
         <v>101</v>
       </c>
       <c r="B103" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C103" t="n">
         <v>0</v>
@@ -2658,7 +2658,7 @@
         <v>102</v>
       </c>
       <c r="B104" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C104" t="n">
         <v>0</v>
@@ -2675,7 +2675,7 @@
         <v>103</v>
       </c>
       <c r="B105" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C105" t="n">
         <v>0</v>
@@ -2692,7 +2692,7 @@
         <v>104</v>
       </c>
       <c r="B106" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C106" t="n">
         <v>0</v>
@@ -2709,7 +2709,7 @@
         <v>105</v>
       </c>
       <c r="B107" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C107" t="n">
         <v>0</v>
@@ -2726,7 +2726,7 @@
         <v>106</v>
       </c>
       <c r="B108" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C108" t="n">
         <v>0</v>
@@ -2743,7 +2743,7 @@
         <v>107</v>
       </c>
       <c r="B109" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C109" t="n">
         <v>0</v>
@@ -2760,7 +2760,7 @@
         <v>108</v>
       </c>
       <c r="B110" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C110" t="n">
         <v>0</v>
@@ -2777,7 +2777,7 @@
         <v>109</v>
       </c>
       <c r="B111" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C111" t="n">
         <v>0</v>
@@ -2794,7 +2794,7 @@
         <v>110</v>
       </c>
       <c r="B112" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C112" t="n">
         <v>0</v>
@@ -2811,7 +2811,7 @@
         <v>111</v>
       </c>
       <c r="B113" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C113" t="n">
         <v>0</v>
@@ -2828,7 +2828,7 @@
         <v>112</v>
       </c>
       <c r="B114" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C114" t="n">
         <v>0</v>
@@ -2845,7 +2845,7 @@
         <v>113</v>
       </c>
       <c r="B115" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C115" t="n">
         <v>0</v>
@@ -2862,7 +2862,7 @@
         <v>114</v>
       </c>
       <c r="B116" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C116" t="n">
         <v>0</v>
@@ -2879,7 +2879,7 @@
         <v>115</v>
       </c>
       <c r="B117" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C117" t="n">
         <v>0</v>
@@ -2896,7 +2896,7 @@
         <v>116</v>
       </c>
       <c r="B118" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C118" t="n">
         <v>0</v>
@@ -2913,7 +2913,7 @@
         <v>117</v>
       </c>
       <c r="B119" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C119" t="n">
         <v>0</v>
@@ -2930,7 +2930,7 @@
         <v>118</v>
       </c>
       <c r="B120" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C120" t="n">
         <v>0</v>
@@ -2947,7 +2947,7 @@
         <v>119</v>
       </c>
       <c r="B121" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C121" t="n">
         <v>0</v>
@@ -2964,7 +2964,7 @@
         <v>120</v>
       </c>
       <c r="B122" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C122" t="n">
         <v>0</v>
@@ -2981,7 +2981,7 @@
         <v>121</v>
       </c>
       <c r="B123" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C123" t="n">
         <v>0</v>
@@ -2998,7 +2998,7 @@
         <v>122</v>
       </c>
       <c r="B124" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C124" t="n">
         <v>0</v>
@@ -3015,7 +3015,7 @@
         <v>123</v>
       </c>
       <c r="B125" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C125" t="n">
         <v>0</v>
@@ -3032,7 +3032,7 @@
         <v>124</v>
       </c>
       <c r="B126" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C126" t="n">
         <v>0</v>
@@ -3049,7 +3049,7 @@
         <v>125</v>
       </c>
       <c r="B127" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C127" t="n">
         <v>0</v>
@@ -3066,7 +3066,7 @@
         <v>126</v>
       </c>
       <c r="B128" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C128" t="n">
         <v>0</v>
@@ -3083,7 +3083,7 @@
         <v>127</v>
       </c>
       <c r="B129" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C129" t="n">
         <v>0</v>
@@ -3100,7 +3100,7 @@
         <v>128</v>
       </c>
       <c r="B130" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C130" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
         <v>129</v>
       </c>
       <c r="B131" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C131" t="n">
         <v>0</v>
@@ -3134,7 +3134,7 @@
         <v>130</v>
       </c>
       <c r="B132" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C132" t="n">
         <v>0</v>
@@ -3151,7 +3151,7 @@
         <v>131</v>
       </c>
       <c r="B133" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C133" t="n">
         <v>0</v>
@@ -3168,7 +3168,7 @@
         <v>132</v>
       </c>
       <c r="B134" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C134" t="n">
         <v>0</v>
@@ -3185,7 +3185,7 @@
         <v>133</v>
       </c>
       <c r="B135" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C135" t="n">
         <v>0</v>
@@ -3202,7 +3202,7 @@
         <v>134</v>
       </c>
       <c r="B136" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C136" t="n">
         <v>0</v>
@@ -3219,7 +3219,7 @@
         <v>135</v>
       </c>
       <c r="B137" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C137" t="n">
         <v>0</v>
@@ -3236,7 +3236,7 @@
         <v>136</v>
       </c>
       <c r="B138" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C138" t="n">
         <v>0</v>
@@ -3253,7 +3253,7 @@
         <v>137</v>
       </c>
       <c r="B139" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C139" t="n">
         <v>0</v>
@@ -3270,7 +3270,7 @@
         <v>138</v>
       </c>
       <c r="B140" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C140" t="n">
         <v>0</v>
@@ -3287,7 +3287,7 @@
         <v>139</v>
       </c>
       <c r="B141" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C141" t="n">
         <v>0</v>
@@ -3304,7 +3304,7 @@
         <v>140</v>
       </c>
       <c r="B142" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C142" t="n">
         <v>0</v>
@@ -3321,7 +3321,7 @@
         <v>141</v>
       </c>
       <c r="B143" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C143" t="n">
         <v>0</v>
@@ -3338,7 +3338,7 @@
         <v>142</v>
       </c>
       <c r="B144" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C144" t="n">
         <v>0</v>
@@ -3355,7 +3355,7 @@
         <v>143</v>
       </c>
       <c r="B145" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C145" t="n">
         <v>0</v>
@@ -3372,7 +3372,7 @@
         <v>144</v>
       </c>
       <c r="B146" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C146" t="n">
         <v>0</v>
@@ -3389,7 +3389,7 @@
         <v>145</v>
       </c>
       <c r="B147" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C147" t="n">
         <v>0</v>
@@ -3406,7 +3406,7 @@
         <v>146</v>
       </c>
       <c r="B148" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C148" t="n">
         <v>0</v>
@@ -3423,7 +3423,7 @@
         <v>147</v>
       </c>
       <c r="B149" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C149" t="n">
         <v>0</v>
@@ -3440,7 +3440,7 @@
         <v>148</v>
       </c>
       <c r="B150" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C150" t="n">
         <v>0</v>
@@ -3457,7 +3457,7 @@
         <v>149</v>
       </c>
       <c r="B151" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C151" t="n">
         <v>0</v>
@@ -3474,7 +3474,7 @@
         <v>150</v>
       </c>
       <c r="B152" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C152" t="n">
         <v>0</v>
@@ -3491,7 +3491,7 @@
         <v>151</v>
       </c>
       <c r="B153" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C153" t="n">
         <v>0</v>
@@ -3508,7 +3508,7 @@
         <v>152</v>
       </c>
       <c r="B154" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C154" t="n">
         <v>0</v>
@@ -3525,7 +3525,7 @@
         <v>153</v>
       </c>
       <c r="B155" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C155" t="n">
         <v>0</v>
@@ -3542,7 +3542,7 @@
         <v>154</v>
       </c>
       <c r="B156" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C156" t="n">
         <v>0</v>
@@ -3559,7 +3559,7 @@
         <v>155</v>
       </c>
       <c r="B157" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C157" t="n">
         <v>0</v>
@@ -3576,7 +3576,7 @@
         <v>156</v>
       </c>
       <c r="B158" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C158" t="n">
         <v>0</v>
@@ -3593,7 +3593,7 @@
         <v>157</v>
       </c>
       <c r="B159" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C159" t="n">
         <v>0</v>
@@ -3610,7 +3610,7 @@
         <v>158</v>
       </c>
       <c r="B160" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C160" t="n">
         <v>0</v>
@@ -3627,7 +3627,7 @@
         <v>159</v>
       </c>
       <c r="B161" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C161" t="n">
         <v>0</v>
@@ -3644,7 +3644,7 @@
         <v>160</v>
       </c>
       <c r="B162" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C162" t="n">
         <v>0</v>
@@ -3661,7 +3661,7 @@
         <v>161</v>
       </c>
       <c r="B163" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C163" t="n">
         <v>0</v>
@@ -3678,7 +3678,7 @@
         <v>162</v>
       </c>
       <c r="B164" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C164" t="n">
         <v>0</v>
@@ -3695,7 +3695,7 @@
         <v>163</v>
       </c>
       <c r="B165" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C165" t="n">
         <v>0</v>
@@ -3712,7 +3712,7 @@
         <v>164</v>
       </c>
       <c r="B166" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C166" t="n">
         <v>0</v>
@@ -3729,7 +3729,7 @@
         <v>165</v>
       </c>
       <c r="B167" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C167" t="n">
         <v>0</v>
@@ -3746,7 +3746,7 @@
         <v>166</v>
       </c>
       <c r="B168" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C168" t="n">
         <v>0</v>
@@ -3763,7 +3763,7 @@
         <v>167</v>
       </c>
       <c r="B169" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C169" t="n">
         <v>0</v>
@@ -3780,7 +3780,7 @@
         <v>168</v>
       </c>
       <c r="B170" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C170" t="n">
         <v>0</v>
@@ -3797,7 +3797,7 @@
         <v>169</v>
       </c>
       <c r="B171" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C171" t="n">
         <v>0</v>
@@ -3814,7 +3814,7 @@
         <v>170</v>
       </c>
       <c r="B172" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C172" t="n">
         <v>0</v>
@@ -3831,7 +3831,7 @@
         <v>171</v>
       </c>
       <c r="B173" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C173" t="n">
         <v>0</v>
@@ -3848,7 +3848,7 @@
         <v>172</v>
       </c>
       <c r="B174" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C174" t="n">
         <v>0</v>
@@ -3865,7 +3865,7 @@
         <v>173</v>
       </c>
       <c r="B175" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C175" t="n">
         <v>0</v>
@@ -3882,7 +3882,7 @@
         <v>174</v>
       </c>
       <c r="B176" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C176" t="n">
         <v>0</v>
@@ -3899,7 +3899,7 @@
         <v>175</v>
       </c>
       <c r="B177" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C177" t="n">
         <v>0</v>
@@ -3916,7 +3916,7 @@
         <v>176</v>
       </c>
       <c r="B178" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C178" t="n">
         <v>0</v>
@@ -3933,7 +3933,7 @@
         <v>177</v>
       </c>
       <c r="B179" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C179" t="n">
         <v>0</v>
@@ -3950,7 +3950,7 @@
         <v>178</v>
       </c>
       <c r="B180" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C180" t="n">
         <v>0</v>
@@ -3967,7 +3967,7 @@
         <v>179</v>
       </c>
       <c r="B181" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C181" t="n">
         <v>0</v>
@@ -3984,7 +3984,7 @@
         <v>180</v>
       </c>
       <c r="B182" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C182" t="n">
         <v>0</v>
@@ -4001,7 +4001,7 @@
         <v>181</v>
       </c>
       <c r="B183" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C183" t="n">
         <v>0</v>
@@ -4018,7 +4018,7 @@
         <v>182</v>
       </c>
       <c r="B184" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C184" t="n">
         <v>0</v>
@@ -4035,7 +4035,7 @@
         <v>183</v>
       </c>
       <c r="B185" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C185" t="n">
         <v>0</v>
@@ -4052,7 +4052,7 @@
         <v>184</v>
       </c>
       <c r="B186" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C186" t="n">
         <v>0</v>
@@ -4069,7 +4069,7 @@
         <v>185</v>
       </c>
       <c r="B187" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C187" t="n">
         <v>0</v>
@@ -4086,7 +4086,7 @@
         <v>186</v>
       </c>
       <c r="B188" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C188" t="n">
         <v>0</v>
@@ -4103,7 +4103,7 @@
         <v>187</v>
       </c>
       <c r="B189" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C189" t="n">
         <v>0</v>
@@ -4120,7 +4120,7 @@
         <v>188</v>
       </c>
       <c r="B190" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C190" t="n">
         <v>0</v>
@@ -4137,7 +4137,7 @@
         <v>189</v>
       </c>
       <c r="B191" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C191" t="n">
         <v>0</v>
@@ -4154,7 +4154,7 @@
         <v>190</v>
       </c>
       <c r="B192" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C192" t="n">
         <v>0</v>
@@ -4171,7 +4171,7 @@
         <v>191</v>
       </c>
       <c r="B193" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C193" t="n">
         <v>0</v>
@@ -4188,7 +4188,7 @@
         <v>192</v>
       </c>
       <c r="B194" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C194" t="n">
         <v>0</v>
@@ -4205,7 +4205,7 @@
         <v>193</v>
       </c>
       <c r="B195" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C195" t="n">
         <v>0</v>
@@ -4222,7 +4222,7 @@
         <v>194</v>
       </c>
       <c r="B196" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C196" t="n">
         <v>0</v>
@@ -4239,7 +4239,7 @@
         <v>195</v>
       </c>
       <c r="B197" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C197" t="n">
         <v>0</v>
@@ -4256,7 +4256,7 @@
         <v>196</v>
       </c>
       <c r="B198" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C198" t="n">
         <v>0</v>
@@ -4273,7 +4273,7 @@
         <v>197</v>
       </c>
       <c r="B199" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C199" t="n">
         <v>0</v>
@@ -4290,7 +4290,7 @@
         <v>198</v>
       </c>
       <c r="B200" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C200" t="n">
         <v>0</v>
@@ -4307,7 +4307,7 @@
         <v>199</v>
       </c>
       <c r="B201" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C201" t="n">
         <v>0</v>
@@ -4324,7 +4324,7 @@
         <v>200</v>
       </c>
       <c r="B202" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C202" t="n">
         <v>0</v>
@@ -4341,7 +4341,7 @@
         <v>201</v>
       </c>
       <c r="B203" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C203" t="n">
         <v>0</v>
@@ -4358,7 +4358,7 @@
         <v>202</v>
       </c>
       <c r="B204" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C204" t="n">
         <v>0</v>
@@ -4375,7 +4375,7 @@
         <v>203</v>
       </c>
       <c r="B205" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C205" t="n">
         <v>0</v>
@@ -4392,7 +4392,7 @@
         <v>204</v>
       </c>
       <c r="B206" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C206" t="n">
         <v>0</v>
@@ -4409,7 +4409,7 @@
         <v>205</v>
       </c>
       <c r="B207" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C207" t="n">
         <v>0</v>
@@ -4426,7 +4426,7 @@
         <v>206</v>
       </c>
       <c r="B208" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C208" t="n">
         <v>0</v>
@@ -4443,7 +4443,7 @@
         <v>207</v>
       </c>
       <c r="B209" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C209" t="n">
         <v>0</v>
@@ -4460,7 +4460,7 @@
         <v>208</v>
       </c>
       <c r="B210" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C210" t="n">
         <v>0</v>
@@ -4477,7 +4477,7 @@
         <v>209</v>
       </c>
       <c r="B211" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C211" t="n">
         <v>0</v>
@@ -4494,7 +4494,7 @@
         <v>210</v>
       </c>
       <c r="B212" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C212" t="n">
         <v>0</v>
@@ -4511,7 +4511,7 @@
         <v>211</v>
       </c>
       <c r="B213" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C213" t="n">
         <v>0</v>
@@ -4528,7 +4528,7 @@
         <v>212</v>
       </c>
       <c r="B214" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C214" t="n">
         <v>0</v>
@@ -4545,7 +4545,7 @@
         <v>213</v>
       </c>
       <c r="B215" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C215" t="n">
         <v>0</v>
@@ -4562,7 +4562,7 @@
         <v>214</v>
       </c>
       <c r="B216" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C216" t="n">
         <v>0</v>
@@ -4579,7 +4579,7 @@
         <v>215</v>
       </c>
       <c r="B217" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C217" t="n">
         <v>0</v>
@@ -4596,7 +4596,7 @@
         <v>216</v>
       </c>
       <c r="B218" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C218" t="n">
         <v>0</v>
@@ -4613,7 +4613,7 @@
         <v>217</v>
       </c>
       <c r="B219" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C219" t="n">
         <v>0</v>
@@ -4630,7 +4630,7 @@
         <v>218</v>
       </c>
       <c r="B220" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C220" t="n">
         <v>0</v>
@@ -4647,7 +4647,7 @@
         <v>219</v>
       </c>
       <c r="B221" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C221" t="n">
         <v>0</v>
@@ -4664,7 +4664,7 @@
         <v>220</v>
       </c>
       <c r="B222" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C222" t="n">
         <v>0</v>
@@ -4681,7 +4681,7 @@
         <v>221</v>
       </c>
       <c r="B223" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C223" t="n">
         <v>0</v>
@@ -4698,7 +4698,7 @@
         <v>222</v>
       </c>
       <c r="B224" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C224" t="n">
         <v>0</v>
@@ -4715,7 +4715,7 @@
         <v>223</v>
       </c>
       <c r="B225" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C225" t="n">
         <v>0</v>
@@ -4732,7 +4732,7 @@
         <v>224</v>
       </c>
       <c r="B226" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C226" t="n">
         <v>0</v>
@@ -4749,7 +4749,7 @@
         <v>225</v>
       </c>
       <c r="B227" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C227" t="n">
         <v>0</v>
@@ -4766,7 +4766,7 @@
         <v>226</v>
       </c>
       <c r="B228" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C228" t="n">
         <v>0</v>
@@ -4783,7 +4783,7 @@
         <v>227</v>
       </c>
       <c r="B229" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C229" t="n">
         <v>0</v>
@@ -4800,7 +4800,7 @@
         <v>228</v>
       </c>
       <c r="B230" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C230" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
         <v>229</v>
       </c>
       <c r="B231" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C231" t="n">
         <v>0</v>
@@ -4834,7 +4834,7 @@
         <v>230</v>
       </c>
       <c r="B232" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C232" t="n">
         <v>0</v>
@@ -4851,7 +4851,7 @@
         <v>231</v>
       </c>
       <c r="B233" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C233" t="n">
         <v>0</v>
@@ -4868,7 +4868,7 @@
         <v>232</v>
       </c>
       <c r="B234" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C234" t="n">
         <v>0</v>
@@ -4885,7 +4885,7 @@
         <v>233</v>
       </c>
       <c r="B235" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C235" t="n">
         <v>0</v>
@@ -4902,7 +4902,7 @@
         <v>234</v>
       </c>
       <c r="B236" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C236" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>235</v>
       </c>
       <c r="B237" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C237" t="n">
         <v>0</v>
@@ -4936,7 +4936,7 @@
         <v>236</v>
       </c>
       <c r="B238" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C238" t="n">
         <v>0</v>
@@ -4953,7 +4953,7 @@
         <v>237</v>
       </c>
       <c r="B239" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C239" t="n">
         <v>0</v>
@@ -4970,7 +4970,7 @@
         <v>238</v>
       </c>
       <c r="B240" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C240" t="n">
         <v>0</v>
@@ -4987,7 +4987,7 @@
         <v>239</v>
       </c>
       <c r="B241" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C241" t="n">
         <v>0</v>
@@ -5004,7 +5004,7 @@
         <v>240</v>
       </c>
       <c r="B242" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C242" t="n">
         <v>0</v>
@@ -5021,7 +5021,7 @@
         <v>241</v>
       </c>
       <c r="B243" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C243" t="n">
         <v>0</v>
@@ -5038,7 +5038,7 @@
         <v>242</v>
       </c>
       <c r="B244" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C244" t="n">
         <v>0</v>
@@ -5055,7 +5055,7 @@
         <v>243</v>
       </c>
       <c r="B245" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C245" t="n">
         <v>0</v>
@@ -5072,7 +5072,7 @@
         <v>244</v>
       </c>
       <c r="B246" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C246" t="n">
         <v>0</v>
@@ -5089,7 +5089,7 @@
         <v>245</v>
       </c>
       <c r="B247" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C247" t="n">
         <v>0</v>
@@ -5106,7 +5106,7 @@
         <v>246</v>
       </c>
       <c r="B248" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C248" t="n">
         <v>0</v>
@@ -5123,7 +5123,7 @@
         <v>247</v>
       </c>
       <c r="B249" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C249" t="n">
         <v>0</v>
@@ -5140,7 +5140,7 @@
         <v>248</v>
       </c>
       <c r="B250" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C250" t="n">
         <v>0</v>
@@ -5157,7 +5157,7 @@
         <v>249</v>
       </c>
       <c r="B251" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C251" t="n">
         <v>0</v>
@@ -5174,7 +5174,7 @@
         <v>250</v>
       </c>
       <c r="B252" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C252" t="n">
         <v>0</v>
@@ -5191,7 +5191,7 @@
         <v>251</v>
       </c>
       <c r="B253" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C253" t="n">
         <v>0</v>
@@ -5208,7 +5208,7 @@
         <v>252</v>
       </c>
       <c r="B254" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C254" t="n">
         <v>0</v>
@@ -5225,7 +5225,7 @@
         <v>253</v>
       </c>
       <c r="B255" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C255" t="n">
         <v>0</v>
@@ -5242,7 +5242,7 @@
         <v>254</v>
       </c>
       <c r="B256" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C256" t="n">
         <v>0</v>
@@ -5259,7 +5259,7 @@
         <v>255</v>
       </c>
       <c r="B257" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C257" t="n">
         <v>0</v>
@@ -5276,7 +5276,7 @@
         <v>256</v>
       </c>
       <c r="B258" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C258" t="n">
         <v>0</v>
@@ -5293,7 +5293,7 @@
         <v>257</v>
       </c>
       <c r="B259" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C259" t="n">
         <v>0</v>
@@ -5310,7 +5310,7 @@
         <v>258</v>
       </c>
       <c r="B260" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C260" t="n">
         <v>0</v>
@@ -5327,7 +5327,7 @@
         <v>259</v>
       </c>
       <c r="B261" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C261" t="n">
         <v>0</v>
@@ -5344,7 +5344,7 @@
         <v>260</v>
       </c>
       <c r="B262" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C262" t="n">
         <v>0</v>
@@ -5361,7 +5361,7 @@
         <v>261</v>
       </c>
       <c r="B263" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C263" t="n">
         <v>0</v>
@@ -5378,7 +5378,7 @@
         <v>262</v>
       </c>
       <c r="B264" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C264" t="n">
         <v>0</v>
@@ -5395,7 +5395,7 @@
         <v>263</v>
       </c>
       <c r="B265" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C265" t="n">
         <v>0</v>
@@ -5412,7 +5412,7 @@
         <v>264</v>
       </c>
       <c r="B266" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C266" t="n">
         <v>0</v>
@@ -5429,7 +5429,7 @@
         <v>265</v>
       </c>
       <c r="B267" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C267" t="n">
         <v>0</v>
@@ -5446,7 +5446,7 @@
         <v>266</v>
       </c>
       <c r="B268" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C268" t="n">
         <v>0</v>
@@ -5463,7 +5463,7 @@
         <v>267</v>
       </c>
       <c r="B269" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C269" t="n">
         <v>0</v>
@@ -5480,7 +5480,7 @@
         <v>268</v>
       </c>
       <c r="B270" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C270" t="n">
         <v>0</v>
@@ -5497,7 +5497,7 @@
         <v>269</v>
       </c>
       <c r="B271" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C271" t="n">
         <v>0</v>
@@ -5514,7 +5514,7 @@
         <v>270</v>
       </c>
       <c r="B272" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C272" t="n">
         <v>0</v>
@@ -5531,7 +5531,7 @@
         <v>271</v>
       </c>
       <c r="B273" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C273" t="n">
         <v>0</v>
@@ -5548,7 +5548,7 @@
         <v>272</v>
       </c>
       <c r="B274" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C274" t="n">
         <v>0</v>
@@ -5565,7 +5565,7 @@
         <v>273</v>
       </c>
       <c r="B275" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C275" t="n">
         <v>0</v>
@@ -5582,7 +5582,7 @@
         <v>274</v>
       </c>
       <c r="B276" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C276" t="n">
         <v>0</v>
@@ -5599,7 +5599,7 @@
         <v>275</v>
       </c>
       <c r="B277" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C277" t="n">
         <v>0</v>
@@ -5616,7 +5616,7 @@
         <v>276</v>
       </c>
       <c r="B278" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C278" t="n">
         <v>0</v>
@@ -5633,7 +5633,7 @@
         <v>277</v>
       </c>
       <c r="B279" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C279" t="n">
         <v>0</v>
@@ -5650,7 +5650,7 @@
         <v>278</v>
       </c>
       <c r="B280" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C280" t="n">
         <v>0</v>
@@ -5667,7 +5667,7 @@
         <v>279</v>
       </c>
       <c r="B281" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C281" t="n">
         <v>0</v>
@@ -5684,7 +5684,7 @@
         <v>280</v>
       </c>
       <c r="B282" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C282" t="n">
         <v>0</v>
@@ -5701,7 +5701,7 @@
         <v>281</v>
       </c>
       <c r="B283" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C283" t="n">
         <v>0</v>
@@ -5718,7 +5718,7 @@
         <v>282</v>
       </c>
       <c r="B284" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C284" t="n">
         <v>0</v>
@@ -5735,7 +5735,7 @@
         <v>283</v>
       </c>
       <c r="B285" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C285" t="n">
         <v>0</v>
@@ -5752,7 +5752,7 @@
         <v>284</v>
       </c>
       <c r="B286" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C286" t="n">
         <v>0</v>
@@ -5769,7 +5769,7 @@
         <v>285</v>
       </c>
       <c r="B287" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C287" t="n">
         <v>0</v>
@@ -5786,7 +5786,7 @@
         <v>286</v>
       </c>
       <c r="B288" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C288" t="n">
         <v>0</v>
@@ -5803,7 +5803,7 @@
         <v>287</v>
       </c>
       <c r="B289" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C289" t="n">
         <v>0</v>
@@ -5820,7 +5820,7 @@
         <v>288</v>
       </c>
       <c r="B290" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C290" t="n">
         <v>0</v>
@@ -5837,7 +5837,7 @@
         <v>289</v>
       </c>
       <c r="B291" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C291" t="n">
         <v>0</v>
@@ -5854,7 +5854,7 @@
         <v>290</v>
       </c>
       <c r="B292" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C292" t="n">
         <v>0</v>
@@ -5871,7 +5871,7 @@
         <v>291</v>
       </c>
       <c r="B293" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C293" t="n">
         <v>0</v>
@@ -5888,7 +5888,7 @@
         <v>292</v>
       </c>
       <c r="B294" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C294" t="n">
         <v>0</v>
@@ -5905,7 +5905,7 @@
         <v>293</v>
       </c>
       <c r="B295" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C295" t="n">
         <v>0</v>
@@ -5922,7 +5922,7 @@
         <v>294</v>
       </c>
       <c r="B296" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C296" t="n">
         <v>0</v>
@@ -5939,7 +5939,7 @@
         <v>295</v>
       </c>
       <c r="B297" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C297" t="n">
         <v>0</v>
@@ -5956,7 +5956,7 @@
         <v>296</v>
       </c>
       <c r="B298" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C298" t="n">
         <v>0</v>
@@ -5973,7 +5973,7 @@
         <v>297</v>
       </c>
       <c r="B299" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C299" t="n">
         <v>0</v>
@@ -5990,7 +5990,7 @@
         <v>298</v>
       </c>
       <c r="B300" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C300" t="n">
         <v>0</v>
@@ -6007,7 +6007,7 @@
         <v>299</v>
       </c>
       <c r="B301" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C301" t="n">
         <v>0</v>
@@ -6024,7 +6024,7 @@
         <v>300</v>
       </c>
       <c r="B302" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C302" t="n">
         <v>0</v>
@@ -6041,7 +6041,7 @@
         <v>301</v>
       </c>
       <c r="B303" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C303" t="n">
         <v>0</v>
@@ -6058,7 +6058,7 @@
         <v>302</v>
       </c>
       <c r="B304" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C304" t="n">
         <v>0</v>
@@ -6075,7 +6075,7 @@
         <v>303</v>
       </c>
       <c r="B305" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C305" t="n">
         <v>0</v>
@@ -6092,7 +6092,7 @@
         <v>304</v>
       </c>
       <c r="B306" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C306" t="n">
         <v>0</v>
@@ -6109,7 +6109,7 @@
         <v>305</v>
       </c>
       <c r="B307" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C307" t="n">
         <v>0</v>
@@ -6126,7 +6126,7 @@
         <v>306</v>
       </c>
       <c r="B308" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C308" t="n">
         <v>0</v>
@@ -6143,7 +6143,7 @@
         <v>307</v>
       </c>
       <c r="B309" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C309" t="n">
         <v>0</v>
@@ -6160,7 +6160,7 @@
         <v>308</v>
       </c>
       <c r="B310" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C310" t="n">
         <v>0</v>
@@ -6177,7 +6177,7 @@
         <v>309</v>
       </c>
       <c r="B311" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C311" t="n">
         <v>0</v>
@@ -6194,7 +6194,7 @@
         <v>310</v>
       </c>
       <c r="B312" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C312" t="n">
         <v>0</v>
@@ -6211,7 +6211,7 @@
         <v>311</v>
       </c>
       <c r="B313" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C313" t="n">
         <v>0</v>
@@ -6228,7 +6228,7 @@
         <v>312</v>
       </c>
       <c r="B314" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C314" t="n">
         <v>0</v>
@@ -6245,7 +6245,7 @@
         <v>313</v>
       </c>
       <c r="B315" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C315" t="n">
         <v>0</v>
@@ -6262,7 +6262,7 @@
         <v>314</v>
       </c>
       <c r="B316" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C316" t="n">
         <v>0</v>
@@ -6279,7 +6279,7 @@
         <v>315</v>
       </c>
       <c r="B317" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C317" t="n">
         <v>0</v>
@@ -6296,7 +6296,7 @@
         <v>316</v>
       </c>
       <c r="B318" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C318" t="n">
         <v>0</v>
@@ -6313,7 +6313,7 @@
         <v>317</v>
       </c>
       <c r="B319" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C319" t="n">
         <v>0</v>
@@ -6330,7 +6330,7 @@
         <v>318</v>
       </c>
       <c r="B320" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C320" t="n">
         <v>0</v>
@@ -6347,7 +6347,7 @@
         <v>319</v>
       </c>
       <c r="B321" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C321" t="n">
         <v>0</v>
@@ -6364,7 +6364,7 @@
         <v>320</v>
       </c>
       <c r="B322" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C322" t="n">
         <v>0</v>
@@ -6381,7 +6381,7 @@
         <v>321</v>
       </c>
       <c r="B323" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C323" t="n">
         <v>0</v>
@@ -6398,7 +6398,7 @@
         <v>322</v>
       </c>
       <c r="B324" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C324" t="n">
         <v>0</v>
@@ -6415,7 +6415,7 @@
         <v>323</v>
       </c>
       <c r="B325" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C325" t="n">
         <v>0</v>
@@ -6432,7 +6432,7 @@
         <v>324</v>
       </c>
       <c r="B326" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C326" t="n">
         <v>0</v>
@@ -6449,7 +6449,7 @@
         <v>325</v>
       </c>
       <c r="B327" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C327" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
         <v>326</v>
       </c>
       <c r="B328" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C328" t="n">
         <v>0</v>
@@ -6483,7 +6483,7 @@
         <v>327</v>
       </c>
       <c r="B329" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C329" t="n">
         <v>0</v>
@@ -6500,7 +6500,7 @@
         <v>328</v>
       </c>
       <c r="B330" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C330" t="n">
         <v>0</v>
@@ -6517,7 +6517,7 @@
         <v>329</v>
       </c>
       <c r="B331" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C331" t="n">
         <v>0</v>
@@ -6534,7 +6534,7 @@
         <v>330</v>
       </c>
       <c r="B332" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C332" t="n">
         <v>98.05867982883639</v>
@@ -6551,7 +6551,7 @@
         <v>331</v>
       </c>
       <c r="B333" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C333" t="n">
         <v>98.05867982883639</v>
@@ -6568,7 +6568,7 @@
         <v>332</v>
       </c>
       <c r="B334" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C334" t="n">
         <v>98.05867982883639</v>
@@ -6585,7 +6585,7 @@
         <v>333</v>
       </c>
       <c r="B335" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C335" t="n">
         <v>98.05867982883639</v>
@@ -6602,7 +6602,7 @@
         <v>334</v>
       </c>
       <c r="B336" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C336" t="n">
         <v>98.05867982883639</v>
@@ -6619,7 +6619,7 @@
         <v>335</v>
       </c>
       <c r="B337" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C337" t="n">
         <v>98.05867982883639</v>
@@ -6636,7 +6636,7 @@
         <v>336</v>
       </c>
       <c r="B338" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C338" t="n">
         <v>98.05867982883639</v>
@@ -6653,7 +6653,7 @@
         <v>337</v>
       </c>
       <c r="B339" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C339" t="n">
         <v>98.05867982883639</v>
@@ -6670,7 +6670,7 @@
         <v>338</v>
       </c>
       <c r="B340" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C340" t="n">
         <v>98.05867982883639</v>
@@ -6687,7 +6687,7 @@
         <v>339</v>
       </c>
       <c r="B341" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C341" t="n">
         <v>98.05867982883639</v>
@@ -6704,7 +6704,7 @@
         <v>340</v>
       </c>
       <c r="B342" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C342" t="n">
         <v>98.05867982883639</v>
@@ -6721,7 +6721,7 @@
         <v>341</v>
       </c>
       <c r="B343" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C343" t="n">
         <v>98.05867982883639</v>
@@ -6738,7 +6738,7 @@
         <v>342</v>
       </c>
       <c r="B344" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C344" t="n">
         <v>98.05867982883639</v>
@@ -6755,7 +6755,7 @@
         <v>343</v>
       </c>
       <c r="B345" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C345" t="n">
         <v>98.05867982883639</v>
@@ -6772,7 +6772,7 @@
         <v>344</v>
       </c>
       <c r="B346" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C346" t="n">
         <v>98.05867982883639</v>
@@ -6789,7 +6789,7 @@
         <v>345</v>
       </c>
       <c r="B347" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C347" t="n">
         <v>98.05867982883639</v>
@@ -6806,7 +6806,7 @@
         <v>346</v>
       </c>
       <c r="B348" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C348" t="n">
         <v>98.05867982883639</v>
@@ -6823,7 +6823,7 @@
         <v>347</v>
       </c>
       <c r="B349" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C349" t="n">
         <v>98.05867982883639</v>
@@ -6840,7 +6840,7 @@
         <v>348</v>
       </c>
       <c r="B350" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C350" t="n">
         <v>98.05867982883639</v>
@@ -6857,7 +6857,7 @@
         <v>349</v>
       </c>
       <c r="B351" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C351" t="n">
         <v>98.05867982883639</v>
@@ -6874,7 +6874,7 @@
         <v>350</v>
       </c>
       <c r="B352" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C352" t="n">
         <v>98.05867982883639</v>
@@ -6891,7 +6891,7 @@
         <v>351</v>
       </c>
       <c r="B353" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C353" t="n">
         <v>98.05867982883639</v>
@@ -6908,7 +6908,7 @@
         <v>352</v>
       </c>
       <c r="B354" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C354" t="n">
         <v>98.05867982883639</v>
@@ -6925,7 +6925,7 @@
         <v>353</v>
       </c>
       <c r="B355" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C355" t="n">
         <v>98.05867982883639</v>
@@ -6942,7 +6942,7 @@
         <v>354</v>
       </c>
       <c r="B356" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C356" t="n">
         <v>98.05867982883639</v>
@@ -6959,7 +6959,7 @@
         <v>355</v>
       </c>
       <c r="B357" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C357" t="n">
         <v>98.05867982883639</v>
@@ -6976,7 +6976,7 @@
         <v>356</v>
       </c>
       <c r="B358" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C358" t="n">
         <v>98.05867982883639</v>
@@ -6993,7 +6993,7 @@
         <v>357</v>
       </c>
       <c r="B359" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C359" t="n">
         <v>98.05867982883639</v>
@@ -7010,7 +7010,7 @@
         <v>358</v>
       </c>
       <c r="B360" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C360" t="n">
         <v>98.05867982883639</v>
@@ -7027,7 +7027,7 @@
         <v>359</v>
       </c>
       <c r="B361" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C361" t="n">
         <v>98.05867982883639</v>
@@ -7044,7 +7044,7 @@
         <v>360</v>
       </c>
       <c r="B362" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C362" t="n">
         <v>98.05867982883639</v>
@@ -7061,7 +7061,7 @@
         <v>361</v>
       </c>
       <c r="B363" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C363" t="n">
         <v>98.05867982883639</v>
@@ -7078,7 +7078,7 @@
         <v>362</v>
       </c>
       <c r="B364" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C364" t="n">
         <v>98.05867982883639</v>
@@ -7095,7 +7095,7 @@
         <v>363</v>
       </c>
       <c r="B365" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C365" t="n">
         <v>98.05867982883639</v>
@@ -7112,7 +7112,7 @@
         <v>364</v>
       </c>
       <c r="B366" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C366" t="n">
         <v>98.05867982883639</v>
@@ -7129,7 +7129,7 @@
         <v>365</v>
       </c>
       <c r="B367" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C367" t="n">
         <v>98.05867982883639</v>
@@ -7146,7 +7146,7 @@
         <v>366</v>
       </c>
       <c r="B368" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C368" t="n">
         <v>98.05867982883639</v>
@@ -7163,7 +7163,7 @@
         <v>367</v>
       </c>
       <c r="B369" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C369" t="n">
         <v>98.05867982883639</v>
@@ -7180,7 +7180,7 @@
         <v>368</v>
       </c>
       <c r="B370" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C370" t="n">
         <v>98.05867982883639</v>
@@ -7197,7 +7197,7 @@
         <v>369</v>
       </c>
       <c r="B371" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C371" t="n">
         <v>98.05867982883639</v>
@@ -7214,7 +7214,7 @@
         <v>370</v>
       </c>
       <c r="B372" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C372" t="n">
         <v>98.05867982883639</v>
@@ -7231,7 +7231,7 @@
         <v>371</v>
       </c>
       <c r="B373" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C373" t="n">
         <v>98.05867982883639</v>
@@ -7248,7 +7248,7 @@
         <v>372</v>
       </c>
       <c r="B374" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C374" t="n">
         <v>98.05867982883639</v>
@@ -7265,7 +7265,7 @@
         <v>373</v>
       </c>
       <c r="B375" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C375" t="n">
         <v>98.05867982883639</v>
@@ -7282,7 +7282,7 @@
         <v>374</v>
       </c>
       <c r="B376" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C376" t="n">
         <v>98.05867982883639</v>
@@ -7299,7 +7299,7 @@
         <v>375</v>
       </c>
       <c r="B377" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C377" t="n">
         <v>98.05867982883639</v>
@@ -7316,7 +7316,7 @@
         <v>376</v>
       </c>
       <c r="B378" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C378" t="n">
         <v>98.05867982883639</v>
@@ -7333,7 +7333,7 @@
         <v>377</v>
       </c>
       <c r="B379" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C379" t="n">
         <v>98.05867982883639</v>
@@ -7350,7 +7350,7 @@
         <v>378</v>
       </c>
       <c r="B380" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C380" t="n">
         <v>98.05867982883639</v>
@@ -7367,7 +7367,7 @@
         <v>379</v>
       </c>
       <c r="B381" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C381" t="n">
         <v>98.05867982883639</v>
@@ -7384,7 +7384,7 @@
         <v>380</v>
       </c>
       <c r="B382" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C382" t="n">
         <v>98.05867982883639</v>
@@ -7401,7 +7401,7 @@
         <v>381</v>
       </c>
       <c r="B383" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C383" t="n">
         <v>98.05867982883639</v>
@@ -7418,7 +7418,7 @@
         <v>382</v>
       </c>
       <c r="B384" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C384" t="n">
         <v>98.05867982883639</v>
@@ -7435,7 +7435,7 @@
         <v>383</v>
       </c>
       <c r="B385" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C385" t="n">
         <v>98.05867982883639</v>
@@ -7452,7 +7452,7 @@
         <v>384</v>
       </c>
       <c r="B386" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C386" t="n">
         <v>98.05867982883639</v>
@@ -7469,7 +7469,7 @@
         <v>385</v>
       </c>
       <c r="B387" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C387" t="n">
         <v>98.05867982883639</v>
@@ -7486,7 +7486,7 @@
         <v>386</v>
       </c>
       <c r="B388" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C388" t="n">
         <v>98.05867982883639</v>
@@ -7503,7 +7503,7 @@
         <v>387</v>
       </c>
       <c r="B389" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C389" t="n">
         <v>98.05867982883639</v>
@@ -7520,7 +7520,7 @@
         <v>388</v>
       </c>
       <c r="B390" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C390" t="n">
         <v>98.05867982883639</v>
@@ -7537,7 +7537,7 @@
         <v>389</v>
       </c>
       <c r="B391" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C391" t="n">
         <v>98.05867982883639</v>
@@ -7554,7 +7554,7 @@
         <v>390</v>
       </c>
       <c r="B392" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C392" t="n">
         <v>98.05867982883639</v>
@@ -7571,7 +7571,7 @@
         <v>391</v>
       </c>
       <c r="B393" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C393" t="n">
         <v>98.05867982883639</v>
@@ -7588,7 +7588,7 @@
         <v>392</v>
       </c>
       <c r="B394" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C394" t="n">
         <v>98.05867982883639</v>
@@ -7605,7 +7605,7 @@
         <v>393</v>
       </c>
       <c r="B395" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C395" t="n">
         <v>98.05867982883639</v>
@@ -7622,7 +7622,7 @@
         <v>394</v>
       </c>
       <c r="B396" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C396" t="n">
         <v>98.05867982883639</v>
@@ -7639,7 +7639,7 @@
         <v>395</v>
       </c>
       <c r="B397" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C397" t="n">
         <v>98.05867982883639</v>
@@ -7656,7 +7656,7 @@
         <v>396</v>
       </c>
       <c r="B398" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C398" t="n">
         <v>98.05867982883639</v>
@@ -7673,7 +7673,7 @@
         <v>397</v>
       </c>
       <c r="B399" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C399" t="n">
         <v>98.05867982883639</v>
@@ -7690,7 +7690,7 @@
         <v>398</v>
       </c>
       <c r="B400" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C400" t="n">
         <v>98.05867982883639</v>
@@ -7707,7 +7707,7 @@
         <v>399</v>
       </c>
       <c r="B401" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C401" t="n">
         <v>98.05867982883639</v>
@@ -7724,7 +7724,7 @@
         <v>400</v>
       </c>
       <c r="B402" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C402" t="n">
         <v>98.05867982883639</v>
@@ -7741,7 +7741,7 @@
         <v>401</v>
       </c>
       <c r="B403" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C403" t="n">
         <v>98.05867982883639</v>
@@ -7758,7 +7758,7 @@
         <v>402</v>
       </c>
       <c r="B404" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C404" t="n">
         <v>98.05867982883639</v>
@@ -7775,7 +7775,7 @@
         <v>403</v>
       </c>
       <c r="B405" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C405" t="n">
         <v>98.05867982883639</v>
@@ -7792,7 +7792,7 @@
         <v>404</v>
       </c>
       <c r="B406" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C406" t="n">
         <v>98.05867982883639</v>
@@ -7809,7 +7809,7 @@
         <v>405</v>
       </c>
       <c r="B407" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C407" t="n">
         <v>98.05867982883639</v>
@@ -7826,7 +7826,7 @@
         <v>406</v>
       </c>
       <c r="B408" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C408" t="n">
         <v>98.05867982883639</v>
@@ -7843,7 +7843,7 @@
         <v>407</v>
       </c>
       <c r="B409" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C409" t="n">
         <v>98.05867982883639</v>
@@ -7860,7 +7860,7 @@
         <v>408</v>
       </c>
       <c r="B410" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C410" t="n">
         <v>98.05867982883639</v>
@@ -7877,7 +7877,7 @@
         <v>409</v>
       </c>
       <c r="B411" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C411" t="n">
         <v>98.05867982883639</v>
@@ -7894,7 +7894,7 @@
         <v>410</v>
       </c>
       <c r="B412" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C412" t="n">
         <v>98.05867982883639</v>
@@ -7911,7 +7911,7 @@
         <v>411</v>
       </c>
       <c r="B413" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C413" t="n">
         <v>98.05867982883639</v>
@@ -7928,7 +7928,7 @@
         <v>412</v>
       </c>
       <c r="B414" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C414" t="n">
         <v>98.05867982883639</v>
@@ -7945,7 +7945,7 @@
         <v>413</v>
       </c>
       <c r="B415" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C415" t="n">
         <v>98.05867982883639</v>
@@ -7962,7 +7962,7 @@
         <v>414</v>
       </c>
       <c r="B416" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C416" t="n">
         <v>98.05867982883639</v>
@@ -7979,7 +7979,7 @@
         <v>415</v>
       </c>
       <c r="B417" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C417" t="n">
         <v>98.05867982883639</v>
@@ -7996,7 +7996,7 @@
         <v>416</v>
       </c>
       <c r="B418" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C418" t="n">
         <v>98.05867982883639</v>
@@ -8013,7 +8013,7 @@
         <v>417</v>
       </c>
       <c r="B419" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C419" t="n">
         <v>98.05867982883639</v>
@@ -8030,7 +8030,7 @@
         <v>418</v>
       </c>
       <c r="B420" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C420" t="n">
         <v>98.05867982883639</v>
@@ -8047,7 +8047,7 @@
         <v>419</v>
       </c>
       <c r="B421" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C421" t="n">
         <v>98.05867982883639</v>
@@ -8064,7 +8064,7 @@
         <v>420</v>
       </c>
       <c r="B422" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C422" t="n">
         <v>98.05867982883639</v>
@@ -8081,7 +8081,7 @@
         <v>421</v>
       </c>
       <c r="B423" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C423" t="n">
         <v>98.05867982883639</v>
@@ -8098,7 +8098,7 @@
         <v>422</v>
       </c>
       <c r="B424" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C424" t="n">
         <v>98.05867982883639</v>
@@ -8115,7 +8115,7 @@
         <v>423</v>
       </c>
       <c r="B425" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C425" t="n">
         <v>98.05867982883639</v>
@@ -8132,7 +8132,7 @@
         <v>424</v>
       </c>
       <c r="B426" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C426" t="n">
         <v>98.05867982883639</v>
@@ -8149,7 +8149,7 @@
         <v>425</v>
       </c>
       <c r="B427" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C427" t="n">
         <v>98.05867982883639</v>
@@ -8166,7 +8166,7 @@
         <v>426</v>
       </c>
       <c r="B428" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C428" t="n">
         <v>98.05867982883639</v>
@@ -8183,7 +8183,7 @@
         <v>427</v>
       </c>
       <c r="B429" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C429" t="n">
         <v>98.05867982883639</v>
@@ -8200,7 +8200,7 @@
         <v>428</v>
       </c>
       <c r="B430" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C430" t="n">
         <v>98.05867982883639</v>
@@ -8217,7 +8217,7 @@
         <v>429</v>
       </c>
       <c r="B431" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C431" t="n">
         <v>98.05867982883639</v>
@@ -8234,7 +8234,7 @@
         <v>430</v>
       </c>
       <c r="B432" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C432" t="n">
         <v>98.05867982883639</v>
@@ -8251,7 +8251,7 @@
         <v>431</v>
       </c>
       <c r="B433" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C433" t="n">
         <v>98.05867982883639</v>
@@ -8268,7 +8268,7 @@
         <v>432</v>
       </c>
       <c r="B434" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C434" t="n">
         <v>98.05867982883639</v>
@@ -8285,7 +8285,7 @@
         <v>433</v>
       </c>
       <c r="B435" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C435" t="n">
         <v>98.05867982883639</v>
@@ -8302,7 +8302,7 @@
         <v>434</v>
       </c>
       <c r="B436" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C436" t="n">
         <v>98.05867982883639</v>
@@ -22327,7 +22327,7 @@
         <v>1259</v>
       </c>
       <c r="B1261" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1261" t="n">
         <v>0</v>
@@ -22344,7 +22344,7 @@
         <v>1260</v>
       </c>
       <c r="B1262" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1262" t="n">
         <v>0</v>
@@ -22361,7 +22361,7 @@
         <v>1261</v>
       </c>
       <c r="B1263" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1263" t="n">
         <v>0</v>
@@ -22378,7 +22378,7 @@
         <v>1262</v>
       </c>
       <c r="B1264" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1264" t="n">
         <v>0</v>
@@ -22395,7 +22395,7 @@
         <v>1263</v>
       </c>
       <c r="B1265" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1265" t="n">
         <v>0</v>
@@ -22412,7 +22412,7 @@
         <v>1264</v>
       </c>
       <c r="B1266" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1266" t="n">
         <v>0</v>
@@ -22429,7 +22429,7 @@
         <v>1265</v>
       </c>
       <c r="B1267" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1267" t="n">
         <v>0</v>
@@ -22446,7 +22446,7 @@
         <v>1266</v>
       </c>
       <c r="B1268" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1268" t="n">
         <v>0</v>
@@ -22463,7 +22463,7 @@
         <v>1267</v>
       </c>
       <c r="B1269" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1269" t="n">
         <v>0</v>
@@ -22480,7 +22480,7 @@
         <v>1268</v>
       </c>
       <c r="B1270" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1270" t="n">
         <v>0</v>
@@ -22497,7 +22497,7 @@
         <v>1269</v>
       </c>
       <c r="B1271" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1271" t="n">
         <v>0</v>
@@ -22514,7 +22514,7 @@
         <v>1270</v>
       </c>
       <c r="B1272" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1272" t="n">
         <v>0</v>
@@ -22531,7 +22531,7 @@
         <v>1271</v>
       </c>
       <c r="B1273" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1273" t="n">
         <v>0</v>
@@ -22548,7 +22548,7 @@
         <v>1272</v>
       </c>
       <c r="B1274" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1274" t="n">
         <v>0</v>
@@ -22565,7 +22565,7 @@
         <v>1273</v>
       </c>
       <c r="B1275" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1275" t="n">
         <v>0</v>
@@ -22582,7 +22582,7 @@
         <v>1274</v>
       </c>
       <c r="B1276" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1276" t="n">
         <v>0</v>
@@ -22599,7 +22599,7 @@
         <v>1275</v>
       </c>
       <c r="B1277" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1277" t="n">
         <v>0</v>
@@ -22616,7 +22616,7 @@
         <v>1276</v>
       </c>
       <c r="B1278" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1278" t="n">
         <v>0</v>
@@ -22633,7 +22633,7 @@
         <v>1277</v>
       </c>
       <c r="B1279" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1279" t="n">
         <v>0</v>
@@ -22650,7 +22650,7 @@
         <v>1278</v>
       </c>
       <c r="B1280" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1280" t="n">
         <v>0</v>
@@ -22667,7 +22667,7 @@
         <v>1279</v>
       </c>
       <c r="B1281" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1281" t="n">
         <v>0</v>
@@ -22684,7 +22684,7 @@
         <v>1280</v>
       </c>
       <c r="B1282" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1282" t="n">
         <v>0</v>
@@ -22701,7 +22701,7 @@
         <v>1281</v>
       </c>
       <c r="B1283" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1283" t="n">
         <v>0</v>
@@ -22718,7 +22718,7 @@
         <v>1282</v>
       </c>
       <c r="B1284" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1284" t="n">
         <v>0</v>
@@ -22735,7 +22735,7 @@
         <v>1283</v>
       </c>
       <c r="B1285" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1285" t="n">
         <v>0</v>
@@ -22752,7 +22752,7 @@
         <v>1284</v>
       </c>
       <c r="B1286" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1286" t="n">
         <v>0</v>
@@ -22769,7 +22769,7 @@
         <v>1285</v>
       </c>
       <c r="B1287" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1287" t="n">
         <v>0</v>
@@ -22786,7 +22786,7 @@
         <v>1286</v>
       </c>
       <c r="B1288" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1288" t="n">
         <v>0</v>
@@ -22803,7 +22803,7 @@
         <v>1287</v>
       </c>
       <c r="B1289" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1289" t="n">
         <v>0</v>
@@ -22820,7 +22820,7 @@
         <v>1288</v>
       </c>
       <c r="B1290" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1290" t="n">
         <v>0</v>
@@ -22837,7 +22837,7 @@
         <v>1289</v>
       </c>
       <c r="B1291" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1291" t="n">
         <v>0</v>
@@ -22854,7 +22854,7 @@
         <v>1290</v>
       </c>
       <c r="B1292" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1292" t="n">
         <v>0</v>
@@ -22871,7 +22871,7 @@
         <v>1291</v>
       </c>
       <c r="B1293" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1293" t="n">
         <v>0</v>
@@ -22888,7 +22888,7 @@
         <v>1292</v>
       </c>
       <c r="B1294" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1294" t="n">
         <v>0</v>
@@ -22905,7 +22905,7 @@
         <v>1293</v>
       </c>
       <c r="B1295" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1295" t="n">
         <v>0</v>
@@ -22922,7 +22922,7 @@
         <v>1294</v>
       </c>
       <c r="B1296" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1296" t="n">
         <v>0</v>
@@ -22939,7 +22939,7 @@
         <v>1295</v>
       </c>
       <c r="B1297" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1297" t="n">
         <v>0</v>
@@ -22956,7 +22956,7 @@
         <v>1296</v>
       </c>
       <c r="B1298" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1298" t="n">
         <v>0</v>
@@ -22973,7 +22973,7 @@
         <v>1297</v>
       </c>
       <c r="B1299" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1299" t="n">
         <v>0</v>
@@ -22990,7 +22990,7 @@
         <v>1298</v>
       </c>
       <c r="B1300" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1300" t="n">
         <v>0</v>
@@ -23007,7 +23007,7 @@
         <v>1299</v>
       </c>
       <c r="B1301" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1301" t="n">
         <v>0</v>
@@ -23024,7 +23024,7 @@
         <v>1300</v>
       </c>
       <c r="B1302" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1302" t="n">
         <v>0</v>
@@ -23041,7 +23041,7 @@
         <v>1301</v>
       </c>
       <c r="B1303" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1303" t="n">
         <v>0</v>
@@ -23058,7 +23058,7 @@
         <v>1302</v>
       </c>
       <c r="B1304" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1304" t="n">
         <v>0</v>
@@ -23075,7 +23075,7 @@
         <v>1303</v>
       </c>
       <c r="B1305" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1305" t="n">
         <v>0</v>
@@ -23092,7 +23092,7 @@
         <v>1304</v>
       </c>
       <c r="B1306" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1306" t="n">
         <v>0</v>
@@ -23109,7 +23109,7 @@
         <v>1305</v>
       </c>
       <c r="B1307" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1307" t="n">
         <v>0</v>
@@ -23126,7 +23126,7 @@
         <v>1306</v>
       </c>
       <c r="B1308" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1308" t="n">
         <v>0</v>
@@ -23143,7 +23143,7 @@
         <v>1307</v>
       </c>
       <c r="B1309" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1309" t="n">
         <v>0</v>
@@ -23160,7 +23160,7 @@
         <v>1308</v>
       </c>
       <c r="B1310" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1310" t="n">
         <v>0</v>
@@ -23177,7 +23177,7 @@
         <v>1309</v>
       </c>
       <c r="B1311" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1311" t="n">
         <v>0</v>
@@ -23194,7 +23194,7 @@
         <v>1310</v>
       </c>
       <c r="B1312" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1312" t="n">
         <v>0</v>
@@ -23211,7 +23211,7 @@
         <v>1311</v>
       </c>
       <c r="B1313" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1313" t="n">
         <v>0</v>
@@ -23228,7 +23228,7 @@
         <v>1312</v>
       </c>
       <c r="B1314" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1314" t="n">
         <v>0</v>
@@ -23245,7 +23245,7 @@
         <v>1313</v>
       </c>
       <c r="B1315" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1315" t="n">
         <v>0</v>
@@ -23262,7 +23262,7 @@
         <v>1314</v>
       </c>
       <c r="B1316" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1316" t="n">
         <v>0</v>
@@ -23279,7 +23279,7 @@
         <v>1315</v>
       </c>
       <c r="B1317" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1317" t="n">
         <v>0</v>
@@ -23296,7 +23296,7 @@
         <v>1316</v>
       </c>
       <c r="B1318" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1318" t="n">
         <v>0</v>
@@ -23313,7 +23313,7 @@
         <v>1317</v>
       </c>
       <c r="B1319" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1319" t="n">
         <v>0</v>
@@ -23330,7 +23330,7 @@
         <v>1318</v>
       </c>
       <c r="B1320" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1320" t="n">
         <v>0</v>
@@ -23347,7 +23347,7 @@
         <v>1319</v>
       </c>
       <c r="B1321" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1321" t="n">
         <v>0</v>
@@ -23364,7 +23364,7 @@
         <v>1320</v>
       </c>
       <c r="B1322" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1322" t="n">
         <v>0</v>
@@ -23381,7 +23381,7 @@
         <v>1321</v>
       </c>
       <c r="B1323" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1323" t="n">
         <v>0</v>
@@ -23398,7 +23398,7 @@
         <v>1322</v>
       </c>
       <c r="B1324" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1324" t="n">
         <v>0</v>
@@ -23415,7 +23415,7 @@
         <v>1323</v>
       </c>
       <c r="B1325" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1325" t="n">
         <v>0</v>
@@ -23432,7 +23432,7 @@
         <v>1324</v>
       </c>
       <c r="B1326" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1326" t="n">
         <v>0</v>
@@ -23449,7 +23449,7 @@
         <v>1325</v>
       </c>
       <c r="B1327" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1327" t="n">
         <v>0</v>
@@ -23466,7 +23466,7 @@
         <v>1326</v>
       </c>
       <c r="B1328" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1328" t="n">
         <v>0</v>
@@ -23483,7 +23483,7 @@
         <v>1327</v>
       </c>
       <c r="B1329" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1329" t="n">
         <v>0</v>
@@ -23500,7 +23500,7 @@
         <v>1328</v>
       </c>
       <c r="B1330" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1330" t="n">
         <v>0</v>
@@ -23517,7 +23517,7 @@
         <v>1329</v>
       </c>
       <c r="B1331" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1331" t="n">
         <v>0</v>
@@ -23534,7 +23534,7 @@
         <v>1330</v>
       </c>
       <c r="B1332" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1332" t="n">
         <v>0</v>
@@ -23551,7 +23551,7 @@
         <v>1331</v>
       </c>
       <c r="B1333" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1333" t="n">
         <v>0</v>
@@ -23568,7 +23568,7 @@
         <v>1332</v>
       </c>
       <c r="B1334" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1334" t="n">
         <v>0</v>
@@ -23585,7 +23585,7 @@
         <v>1333</v>
       </c>
       <c r="B1335" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1335" t="n">
         <v>0</v>
@@ -23602,7 +23602,7 @@
         <v>1334</v>
       </c>
       <c r="B1336" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1336" t="n">
         <v>0</v>
@@ -23619,7 +23619,7 @@
         <v>1335</v>
       </c>
       <c r="B1337" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1337" t="n">
         <v>0</v>
@@ -23636,7 +23636,7 @@
         <v>1336</v>
       </c>
       <c r="B1338" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1338" t="n">
         <v>0</v>
@@ -23653,7 +23653,7 @@
         <v>1337</v>
       </c>
       <c r="B1339" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1339" t="n">
         <v>0</v>
@@ -23670,7 +23670,7 @@
         <v>1338</v>
       </c>
       <c r="B1340" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1340" t="n">
         <v>0</v>
@@ -23687,7 +23687,7 @@
         <v>1339</v>
       </c>
       <c r="B1341" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1341" t="n">
         <v>0</v>
@@ -23704,7 +23704,7 @@
         <v>1340</v>
       </c>
       <c r="B1342" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1342" t="n">
         <v>0</v>
@@ -23721,7 +23721,7 @@
         <v>1341</v>
       </c>
       <c r="B1343" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1343" t="n">
         <v>0</v>
@@ -23738,7 +23738,7 @@
         <v>1342</v>
       </c>
       <c r="B1344" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1344" t="n">
         <v>0</v>
@@ -23755,7 +23755,7 @@
         <v>1343</v>
       </c>
       <c r="B1345" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1345" t="n">
         <v>0</v>
@@ -23772,7 +23772,7 @@
         <v>1344</v>
       </c>
       <c r="B1346" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1346" t="n">
         <v>0</v>
@@ -23789,7 +23789,7 @@
         <v>1345</v>
       </c>
       <c r="B1347" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1347" t="n">
         <v>0</v>
@@ -23806,7 +23806,7 @@
         <v>1346</v>
       </c>
       <c r="B1348" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1348" t="n">
         <v>0</v>
@@ -23823,7 +23823,7 @@
         <v>1347</v>
       </c>
       <c r="B1349" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1349" t="n">
         <v>0</v>
@@ -23840,7 +23840,7 @@
         <v>1348</v>
       </c>
       <c r="B1350" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1350" t="n">
         <v>0</v>
@@ -23857,7 +23857,7 @@
         <v>1349</v>
       </c>
       <c r="B1351" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1351" t="n">
         <v>0</v>
@@ -23874,7 +23874,7 @@
         <v>1350</v>
       </c>
       <c r="B1352" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1352" t="n">
         <v>0</v>
@@ -23891,7 +23891,7 @@
         <v>1351</v>
       </c>
       <c r="B1353" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1353" t="n">
         <v>0</v>
@@ -23908,7 +23908,7 @@
         <v>1352</v>
       </c>
       <c r="B1354" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1354" t="n">
         <v>0</v>
@@ -23925,7 +23925,7 @@
         <v>1353</v>
       </c>
       <c r="B1355" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1355" t="n">
         <v>0</v>
@@ -23942,7 +23942,7 @@
         <v>1354</v>
       </c>
       <c r="B1356" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1356" t="n">
         <v>0</v>
@@ -23959,7 +23959,7 @@
         <v>1355</v>
       </c>
       <c r="B1357" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1357" t="n">
         <v>0</v>
@@ -23976,7 +23976,7 @@
         <v>1356</v>
       </c>
       <c r="B1358" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1358" t="n">
         <v>0</v>
@@ -23993,7 +23993,7 @@
         <v>1357</v>
       </c>
       <c r="B1359" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1359" t="n">
         <v>0</v>
@@ -24010,7 +24010,7 @@
         <v>1358</v>
       </c>
       <c r="B1360" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1360" t="n">
         <v>0</v>
@@ -24027,7 +24027,7 @@
         <v>1359</v>
       </c>
       <c r="B1361" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1361" t="n">
         <v>0</v>
@@ -24044,7 +24044,7 @@
         <v>1360</v>
       </c>
       <c r="B1362" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1362" t="n">
         <v>0</v>
@@ -24061,7 +24061,7 @@
         <v>1361</v>
       </c>
       <c r="B1363" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1363" t="n">
         <v>0</v>
@@ -24078,7 +24078,7 @@
         <v>1362</v>
       </c>
       <c r="B1364" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1364" t="n">
         <v>0</v>
@@ -24095,7 +24095,7 @@
         <v>1363</v>
       </c>
       <c r="B1365" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1365" t="n">
         <v>0</v>
@@ -24112,7 +24112,7 @@
         <v>1364</v>
       </c>
       <c r="B1366" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1366" t="n">
         <v>0</v>
@@ -24129,7 +24129,7 @@
         <v>1365</v>
       </c>
       <c r="B1367" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1367" t="n">
         <v>0</v>
@@ -24146,7 +24146,7 @@
         <v>1366</v>
       </c>
       <c r="B1368" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1368" t="n">
         <v>0</v>
@@ -24163,7 +24163,7 @@
         <v>1367</v>
       </c>
       <c r="B1369" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1369" t="n">
         <v>0</v>
@@ -24180,7 +24180,7 @@
         <v>1368</v>
       </c>
       <c r="B1370" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1370" t="n">
         <v>0</v>
@@ -24197,7 +24197,7 @@
         <v>1369</v>
       </c>
       <c r="B1371" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1371" t="n">
         <v>0</v>
@@ -24214,7 +24214,7 @@
         <v>1370</v>
       </c>
       <c r="B1372" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1372" t="n">
         <v>0</v>
@@ -24231,7 +24231,7 @@
         <v>1371</v>
       </c>
       <c r="B1373" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1373" t="n">
         <v>0</v>
@@ -24248,7 +24248,7 @@
         <v>1372</v>
       </c>
       <c r="B1374" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1374" t="n">
         <v>0</v>
@@ -24265,7 +24265,7 @@
         <v>1373</v>
       </c>
       <c r="B1375" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1375" t="n">
         <v>0</v>
@@ -24282,7 +24282,7 @@
         <v>1374</v>
       </c>
       <c r="B1376" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1376" t="n">
         <v>0</v>
@@ -24299,7 +24299,7 @@
         <v>1375</v>
       </c>
       <c r="B1377" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1377" t="n">
         <v>0</v>
@@ -24316,7 +24316,7 @@
         <v>1376</v>
       </c>
       <c r="B1378" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1378" t="n">
         <v>0</v>
@@ -24333,7 +24333,7 @@
         <v>1377</v>
       </c>
       <c r="B1379" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1379" t="n">
         <v>0</v>
@@ -24350,7 +24350,7 @@
         <v>1378</v>
       </c>
       <c r="B1380" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1380" t="n">
         <v>0</v>
@@ -24367,7 +24367,7 @@
         <v>1379</v>
       </c>
       <c r="B1381" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1381" t="n">
         <v>0</v>
@@ -24384,7 +24384,7 @@
         <v>1380</v>
       </c>
       <c r="B1382" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1382" t="n">
         <v>0</v>
@@ -24401,7 +24401,7 @@
         <v>1381</v>
       </c>
       <c r="B1383" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1383" t="n">
         <v>0</v>
@@ -24418,7 +24418,7 @@
         <v>1382</v>
       </c>
       <c r="B1384" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1384" t="n">
         <v>0</v>
@@ -24435,7 +24435,7 @@
         <v>1383</v>
       </c>
       <c r="B1385" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1385" t="n">
         <v>0</v>
@@ -24452,7 +24452,7 @@
         <v>1384</v>
       </c>
       <c r="B1386" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1386" t="n">
         <v>0</v>
@@ -24469,7 +24469,7 @@
         <v>1385</v>
       </c>
       <c r="B1387" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1387" t="n">
         <v>0</v>
@@ -24486,7 +24486,7 @@
         <v>1386</v>
       </c>
       <c r="B1388" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1388" t="n">
         <v>0</v>
@@ -24503,7 +24503,7 @@
         <v>1387</v>
       </c>
       <c r="B1389" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1389" t="n">
         <v>0</v>
@@ -24520,7 +24520,7 @@
         <v>1388</v>
       </c>
       <c r="B1390" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1390" t="n">
         <v>0</v>
@@ -24537,7 +24537,7 @@
         <v>1389</v>
       </c>
       <c r="B1391" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1391" t="n">
         <v>0</v>
@@ -24554,7 +24554,7 @@
         <v>1390</v>
       </c>
       <c r="B1392" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1392" t="n">
         <v>0</v>
@@ -24571,7 +24571,7 @@
         <v>1391</v>
       </c>
       <c r="B1393" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1393" t="n">
         <v>0</v>
@@ -24588,7 +24588,7 @@
         <v>1392</v>
       </c>
       <c r="B1394" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1394" t="n">
         <v>0</v>
@@ -24605,7 +24605,7 @@
         <v>1393</v>
       </c>
       <c r="B1395" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1395" t="n">
         <v>0</v>
@@ -24622,7 +24622,7 @@
         <v>1394</v>
       </c>
       <c r="B1396" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1396" t="n">
         <v>0</v>
@@ -24639,7 +24639,7 @@
         <v>1395</v>
       </c>
       <c r="B1397" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1397" t="n">
         <v>0</v>
@@ -24656,7 +24656,7 @@
         <v>1396</v>
       </c>
       <c r="B1398" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1398" t="n">
         <v>0</v>
@@ -24673,7 +24673,7 @@
         <v>1397</v>
       </c>
       <c r="B1399" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1399" t="n">
         <v>0</v>
@@ -24690,7 +24690,7 @@
         <v>1398</v>
       </c>
       <c r="B1400" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1400" t="n">
         <v>0</v>
@@ -24707,7 +24707,7 @@
         <v>1399</v>
       </c>
       <c r="B1401" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1401" t="n">
         <v>0</v>
@@ -24724,7 +24724,7 @@
         <v>1400</v>
       </c>
       <c r="B1402" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1402" t="n">
         <v>0</v>
@@ -24741,7 +24741,7 @@
         <v>1401</v>
       </c>
       <c r="B1403" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1403" t="n">
         <v>0</v>
@@ -24758,7 +24758,7 @@
         <v>1402</v>
       </c>
       <c r="B1404" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1404" t="n">
         <v>0</v>
@@ -24775,7 +24775,7 @@
         <v>1403</v>
       </c>
       <c r="B1405" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1405" t="n">
         <v>0</v>
@@ -24792,7 +24792,7 @@
         <v>1404</v>
       </c>
       <c r="B1406" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1406" t="n">
         <v>0</v>
@@ -24809,7 +24809,7 @@
         <v>1405</v>
       </c>
       <c r="B1407" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1407" t="n">
         <v>0</v>
@@ -24826,7 +24826,7 @@
         <v>1406</v>
       </c>
       <c r="B1408" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1408" t="n">
         <v>0</v>
@@ -24843,7 +24843,7 @@
         <v>1407</v>
       </c>
       <c r="B1409" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1409" t="n">
         <v>0</v>
@@ -24860,7 +24860,7 @@
         <v>1408</v>
       </c>
       <c r="B1410" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1410" t="n">
         <v>0</v>
@@ -24877,7 +24877,7 @@
         <v>1409</v>
       </c>
       <c r="B1411" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1411" t="n">
         <v>0</v>
@@ -24894,7 +24894,7 @@
         <v>1410</v>
       </c>
       <c r="B1412" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1412" t="n">
         <v>0</v>
@@ -24911,7 +24911,7 @@
         <v>1411</v>
       </c>
       <c r="B1413" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1413" t="n">
         <v>0</v>
@@ -24928,7 +24928,7 @@
         <v>1412</v>
       </c>
       <c r="B1414" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1414" t="n">
         <v>0</v>
@@ -24945,7 +24945,7 @@
         <v>1413</v>
       </c>
       <c r="B1415" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1415" t="n">
         <v>0</v>
@@ -24962,7 +24962,7 @@
         <v>1414</v>
       </c>
       <c r="B1416" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1416" t="n">
         <v>0</v>
@@ -24979,7 +24979,7 @@
         <v>1415</v>
       </c>
       <c r="B1417" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1417" t="n">
         <v>0</v>
@@ -24996,7 +24996,7 @@
         <v>1416</v>
       </c>
       <c r="B1418" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1418" t="n">
         <v>0</v>
@@ -25013,7 +25013,7 @@
         <v>1417</v>
       </c>
       <c r="B1419" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1419" t="n">
         <v>0</v>
@@ -25030,7 +25030,7 @@
         <v>1418</v>
       </c>
       <c r="B1420" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1420" t="n">
         <v>0</v>
@@ -25047,7 +25047,7 @@
         <v>1419</v>
       </c>
       <c r="B1421" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1421" t="n">
         <v>0</v>
@@ -25064,7 +25064,7 @@
         <v>1420</v>
       </c>
       <c r="B1422" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1422" t="n">
         <v>0</v>
@@ -25081,7 +25081,7 @@
         <v>1421</v>
       </c>
       <c r="B1423" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1423" t="n">
         <v>0</v>
@@ -25098,7 +25098,7 @@
         <v>1422</v>
       </c>
       <c r="B1424" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1424" t="n">
         <v>0</v>
@@ -25115,7 +25115,7 @@
         <v>1423</v>
       </c>
       <c r="B1425" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1425" t="n">
         <v>0</v>
@@ -25132,7 +25132,7 @@
         <v>1424</v>
       </c>
       <c r="B1426" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1426" t="n">
         <v>0</v>
@@ -25149,7 +25149,7 @@
         <v>1425</v>
       </c>
       <c r="B1427" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1427" t="n">
         <v>0</v>
@@ -25166,7 +25166,7 @@
         <v>1426</v>
       </c>
       <c r="B1428" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1428" t="n">
         <v>0</v>
@@ -25183,7 +25183,7 @@
         <v>1427</v>
       </c>
       <c r="B1429" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1429" t="n">
         <v>0</v>
@@ -25200,7 +25200,7 @@
         <v>1428</v>
       </c>
       <c r="B1430" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1430" t="n">
         <v>0</v>
@@ -25217,7 +25217,7 @@
         <v>1429</v>
       </c>
       <c r="B1431" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1431" t="n">
         <v>0</v>
@@ -25234,7 +25234,7 @@
         <v>1430</v>
       </c>
       <c r="B1432" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1432" t="n">
         <v>0</v>
@@ -25251,7 +25251,7 @@
         <v>1431</v>
       </c>
       <c r="B1433" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1433" t="n">
         <v>0</v>
@@ -25268,7 +25268,7 @@
         <v>1432</v>
       </c>
       <c r="B1434" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1434" t="n">
         <v>0</v>
@@ -25285,7 +25285,7 @@
         <v>1433</v>
       </c>
       <c r="B1435" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1435" t="n">
         <v>0</v>
@@ -25302,7 +25302,7 @@
         <v>1434</v>
       </c>
       <c r="B1436" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1436" t="n">
         <v>0</v>
@@ -25319,7 +25319,7 @@
         <v>1435</v>
       </c>
       <c r="B1437" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1437" t="n">
         <v>0</v>
@@ -25336,7 +25336,7 @@
         <v>1436</v>
       </c>
       <c r="B1438" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1438" t="n">
         <v>0</v>
@@ -25353,7 +25353,7 @@
         <v>1437</v>
       </c>
       <c r="B1439" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1439" t="n">
         <v>0</v>
@@ -25370,7 +25370,7 @@
         <v>1438</v>
       </c>
       <c r="B1440" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C1440" t="n">
         <v>0</v>
@@ -25435,7 +25435,7 @@
         <v>46133</v>
       </c>
       <c r="B2" t="n">
-        <v>822.0418053521502</v>
+        <v>1221.269604579949</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -25446,7 +25446,7 @@
         <v>46133.01041666666</v>
       </c>
       <c r="B3" t="n">
-        <v>807.2316555166188</v>
+        <v>1206.844058617394</v>
       </c>
       <c r="C3" t="n">
         <v>15</v>
@@ -25457,7 +25457,7 @@
         <v>46133.02083333334</v>
       </c>
       <c r="B4" t="n">
-        <v>804.967252017086</v>
+        <v>1203.416864420187</v>
       </c>
       <c r="C4" t="n">
         <v>30</v>
@@ -25468,7 +25468,7 @@
         <v>46133.03125</v>
       </c>
       <c r="B5" t="n">
-        <v>805.6970963135346</v>
+        <v>1204.538795155233</v>
       </c>
       <c r="C5" t="n">
         <v>45</v>
@@ -25479,7 +25479,7 @@
         <v>46133.04166666666</v>
       </c>
       <c r="B6" t="n">
-        <v>804.1526947691332</v>
+        <v>1202.222192838631</v>
       </c>
       <c r="C6" t="n">
         <v>60</v>
@@ -25490,7 +25490,7 @@
         <v>46133.05208333334</v>
       </c>
       <c r="B7" t="n">
-        <v>802.6484733428256</v>
+        <v>1199.935295048252</v>
       </c>
       <c r="C7" t="n">
         <v>75</v>
@@ -25501,7 +25501,7 @@
         <v>46133.0625</v>
       </c>
       <c r="B8" t="n">
-        <v>805.6833976833976</v>
+        <v>1204.525096525096</v>
       </c>
       <c r="C8" t="n">
         <v>90</v>
@@ -25512,7 +25512,7 @@
         <v>46133.07291666666</v>
       </c>
       <c r="B9" t="n">
-        <v>806.4760066188637</v>
+        <v>1205.703805846663</v>
       </c>
       <c r="C9" t="n">
         <v>105</v>
@@ -25523,7 +25523,7 @@
         <v>46133.08333333334</v>
       </c>
       <c r="B10" t="n">
-        <v>799.5057915057914</v>
+        <v>1195.258687258687</v>
       </c>
       <c r="C10" t="n">
         <v>120</v>
@@ -25534,7 +25534,7 @@
         <v>46133.09375</v>
       </c>
       <c r="B11" t="n">
-        <v>808.0068493150685</v>
+        <v>1208.006849315068</v>
       </c>
       <c r="C11" t="n">
         <v>135</v>
@@ -25545,7 +25545,7 @@
         <v>46133.10416666666</v>
       </c>
       <c r="B12" t="n">
-        <v>807.2490007676221</v>
+        <v>1206.859895709256</v>
       </c>
       <c r="C12" t="n">
         <v>150</v>
@@ -25556,7 +25556,7 @@
         <v>46133.11458333334</v>
       </c>
       <c r="B13" t="n">
-        <v>805.721697370493</v>
+        <v>1204.572272083137</v>
       </c>
       <c r="C13" t="n">
         <v>165</v>
@@ -25567,7 +25567,7 @@
         <v>46133.125</v>
       </c>
       <c r="B14" t="n">
-        <v>800.2847949990806</v>
+        <v>1196.423791138077</v>
       </c>
       <c r="C14" t="n">
         <v>180</v>
@@ -25578,7 +25578,7 @@
         <v>46133.13541666666</v>
       </c>
       <c r="B15" t="n">
-        <v>799.4932763803195</v>
+        <v>1195.229710488846</v>
       </c>
       <c r="C15" t="n">
         <v>195</v>
@@ -25589,7 +25589,7 @@
         <v>46133.14583333334</v>
       </c>
       <c r="B16" t="n">
-        <v>823.4051633298209</v>
+        <v>1231.097471022129</v>
       </c>
       <c r="C16" t="n">
         <v>210</v>
@@ -25600,7 +25600,7 @@
         <v>46133.15625</v>
       </c>
       <c r="B17" t="n">
-        <v>807.2414978579362</v>
+        <v>1206.855397471836</v>
       </c>
       <c r="C17" t="n">
         <v>225</v>
@@ -25611,7 +25611,7 @@
         <v>46133.16666666666</v>
       </c>
       <c r="B18" t="n">
-        <v>806.4632178452777</v>
+        <v>1205.688024046828</v>
       </c>
       <c r="C18" t="n">
         <v>240</v>
@@ -25622,7 +25622,7 @@
         <v>46133.17708333334</v>
       </c>
       <c r="B19" t="n">
-        <v>787.9364785529169</v>
+        <v>1177.897868514307</v>
       </c>
       <c r="C19" t="n">
         <v>255</v>
@@ -25633,7 +25633,7 @@
         <v>46133.1875</v>
       </c>
       <c r="B20" t="n">
-        <v>805.7107949436715</v>
+        <v>1204.55249378537</v>
       </c>
       <c r="C20" t="n">
         <v>270</v>
@@ -25644,7 +25644,7 @@
         <v>46133.19791666666</v>
       </c>
       <c r="B21" t="n">
-        <v>907.6294442305224</v>
+        <v>1357.440764985239</v>
       </c>
       <c r="C21" t="n">
         <v>285</v>
@@ -25655,7 +25655,7 @@
         <v>46133.20833333334</v>
       </c>
       <c r="B22" t="n">
-        <v>986.5322171486555</v>
+        <v>1475.791476407915</v>
       </c>
       <c r="C22" t="n">
         <v>300</v>
@@ -25666,7 +25666,7 @@
         <v>46133.21875</v>
       </c>
       <c r="B23" t="n">
-        <v>935.3476732851058</v>
+        <v>1399.018085270124</v>
       </c>
       <c r="C23" t="n">
         <v>315</v>
@@ -25677,7 +25677,7 @@
         <v>46133.22916666666</v>
       </c>
       <c r="B24" t="n">
-        <v>824.1674515960228</v>
+        <v>1232.244374672946</v>
       </c>
       <c r="C24" t="n">
         <v>330</v>
@@ -25688,7 +25688,7 @@
         <v>46133.23958333334</v>
       </c>
       <c r="B25" t="n">
-        <v>913.3524283935243</v>
+        <v>1329.261519302615</v>
       </c>
       <c r="C25" t="n">
         <v>345</v>
@@ -25699,7 +25699,7 @@
         <v>46133.25</v>
       </c>
       <c r="B26" t="n">
-        <v>1073.501946115352</v>
+        <v>1559.848809583986</v>
       </c>
       <c r="C26" t="n">
         <v>360</v>
@@ -25710,7 +25710,7 @@
         <v>46133.26041666666</v>
       </c>
       <c r="B27" t="n">
-        <v>1096.045351473923</v>
+        <v>1590.489795918367</v>
       </c>
       <c r="C27" t="n">
         <v>375</v>
@@ -25721,7 +25721,7 @@
         <v>46133.27083333334</v>
       </c>
       <c r="B28" t="n">
-        <v>1085.096924269837</v>
+        <v>1573.39881106229</v>
       </c>
       <c r="C28" t="n">
         <v>390</v>
@@ -25732,7 +25732,7 @@
         <v>46133.28125</v>
       </c>
       <c r="B29" t="n">
-        <v>1093.664960898546</v>
+        <v>1587.15155093686</v>
       </c>
       <c r="C29" t="n">
         <v>405</v>
@@ -25743,7 +25743,7 @@
         <v>46133.29166666666</v>
       </c>
       <c r="B30" t="n">
-        <v>1092.127413127413</v>
+        <v>1584.405405405405</v>
       </c>
       <c r="C30" t="n">
         <v>420</v>
@@ -25754,7 +25754,7 @@
         <v>46133.30208333334</v>
       </c>
       <c r="B31" t="n">
-        <v>1090.374057555485</v>
+        <v>1583.009716470214</v>
       </c>
       <c r="C31" t="n">
         <v>435</v>
@@ -26370,7 +26370,7 @@
         <v>46133.88541666666</v>
       </c>
       <c r="B87" t="n">
-        <v>1234.8</v>
+        <v>1531.74</v>
       </c>
       <c r="C87" t="n">
         <v>1275</v>
@@ -26381,7 +26381,7 @@
         <v>46133.89583333334</v>
       </c>
       <c r="B88" t="n">
-        <v>1263.487464960068</v>
+        <v>1555.490553763156</v>
       </c>
       <c r="C88" t="n">
         <v>1290</v>
@@ -26392,7 +26392,7 @@
         <v>46133.90625</v>
       </c>
       <c r="B89" t="n">
-        <v>1165.860369175438</v>
+        <v>1455.289712804781</v>
       </c>
       <c r="C89" t="n">
         <v>1305</v>
@@ -26403,7 +26403,7 @@
         <v>46133.91666666666</v>
       </c>
       <c r="B90" t="n">
-        <v>1068.906622139381</v>
+        <v>1357.046852024438</v>
       </c>
       <c r="C90" t="n">
         <v>1320</v>
@@ -26414,7 +26414,7 @@
         <v>46133.92708333334</v>
       </c>
       <c r="B91" t="n">
-        <v>1083.176548368329</v>
+        <v>1375.881567673348</v>
       </c>
       <c r="C91" t="n">
         <v>1335</v>
@@ -26425,7 +26425,7 @@
         <v>46133.9375</v>
       </c>
       <c r="B92" t="n">
-        <v>1095.806030520316</v>
+        <v>1392.488656002942</v>
       </c>
       <c r="C92" t="n">
         <v>1350</v>
@@ -26436,7 +26436,7 @@
         <v>46133.94791666666</v>
       </c>
       <c r="B93" t="n">
-        <v>1098.506981541228</v>
+        <v>1396.125514359761</v>
       </c>
       <c r="C93" t="n">
         <v>1365</v>
@@ -26447,7 +26447,7 @@
         <v>46133.95833333334</v>
       </c>
       <c r="B94" t="n">
-        <v>1099.336248682824</v>
+        <v>1396.975479452055</v>
       </c>
       <c r="C94" t="n">
         <v>1380</v>
@@ -26458,7 +26458,7 @@
         <v>46133.96875</v>
       </c>
       <c r="B95" t="n">
-        <v>1098.836647802401</v>
+        <v>1396.221203786957</v>
       </c>
       <c r="C95" t="n">
         <v>1395</v>
@@ -26469,7 +26469,7 @@
         <v>46133.97916666666</v>
       </c>
       <c r="B96" t="n">
-        <v>1113.519764662622</v>
+        <v>1415.583857326715</v>
       </c>
       <c r="C96" t="n">
         <v>1410</v>
@@ -26480,7 +26480,7 @@
         <v>46133.98958333334</v>
       </c>
       <c r="B97" t="n">
-        <v>1107.674274078384</v>
+        <v>1408.100528904638</v>
       </c>
       <c r="C97" t="n">
         <v>1425</v>
@@ -26537,7 +26537,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -26581,7 +26581,7 @@
         <v>435</v>
       </c>
       <c r="B4" t="n">
-        <v>-836.157331737603</v>
+        <v>-1254.235997606404</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -26592,7 +26592,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6.062140655097623</v>
+        <v>9.093210982646427</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
@@ -26691,7 +26691,7 @@
         <v>1259</v>
       </c>
       <c r="B9" t="n">
-        <v>977.4562918987907</v>
+        <v>1270.693179468428</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -26757,7 +26757,7 @@
         <v>1439</v>
       </c>
       <c r="B12" t="n">
-        <v>-977.4562918987907</v>
+        <v>-1270.693179468428</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
@@ -26768,7 +26768,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2.932368875696373</v>
+        <v>3.812079538405284</v>
       </c>
       <c r="F12" t="n">
         <v>1</v>
